--- a/docs/测试/第二次评审/测试材料/01-测试用例总表.xlsx
+++ b/docs/测试/第二次评审/测试材料/01-测试用例总表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,10 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -94,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,6 +115,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -518,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -562,472 +577,498 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>手机号校验·前端</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>手机号校验·后端</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>密码强度</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>客户账号</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>访问控制</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>多商品</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>队列</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>售罄</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>客户账号</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>价格边界</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>意向冲突</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="D18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>越权</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>售罄联动</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>卖家改密</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="D21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>冻结</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>访问控制</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>分页</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="n">
+      <c r="D23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>多商品</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="F23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>库存</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>队列</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>交易</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>售罄</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>价格边界</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3" t="n">
+      <c r="G23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="H23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>意向冲突</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>越权</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>卖家改密</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>冻结</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>分页</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>另 9 条 INCONSISTENT（前后端不一致，见 OBS-014）；手动 23 条已于 2026-10-28 执行完毕</t>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>另 9 条 INCONSISTENT（前后端不一致，见 OBS-014）</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6114,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>售罄</t>
+          <t>售罄联动</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6139,7 +6180,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>售罄</t>
+          <t>售罄联动</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
